--- a/VerveStacks_VNM_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_VNM_grids_kan/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336C037E-4F5C-46D9-AE18-264DEA71CAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176396EE-349A-4534-BE21-DE8B7D90FEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -14529,7 +14529,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F53378-4CA9-4AC6-9F92-7B984DB10E73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FCFB370-7E2F-480D-8FE5-91FB9DE6EE2C}">
   <dimension ref="B3:H1537"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_VNM_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_VNM_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F63BBAA-B2AB-4A63-801C-3F0AC8F99594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073DD4B2-A593-4939-BB25-12E813D0885E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12701,7 +12701,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3C0BC6-F2E5-4CC1-AF9B-77F87EB0BD8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE97F7E-A236-4EE8-AC16-677590306609}">
   <dimension ref="B3:H1537"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_VNM_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_VNM_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073DD4B2-A593-4939-BB25-12E813D0885E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2521CEE0-AA80-4BD4-A3ED-2EE357F4B7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12701,7 +12701,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE97F7E-A236-4EE8-AC16-677590306609}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42774A27-861B-4717-916A-E2C00C77BEBA}">
   <dimension ref="B3:H1537"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
